--- a/data/Study_dates_MeLiDos_FUSPCEU.xlsx
+++ b/data/Study_dates_MeLiDos_FUSPCEU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/WP2.2.5_Data_Analysis/BaezaEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD287A5-9364-9346-AF1C-8C9AA494E304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D366736-3556-D349-9C95-1CDFB0AB3F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="58180" yWindow="9380" windowWidth="29040" windowHeight="15840" xr2:uid="{EB2C5E3B-016F-4147-BA32-349D8E1D3953}"/>
   </bookViews>
@@ -287,6 +287,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="d/m/yy\ h:mm;@"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -361,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -387,9 +390,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -397,6 +397,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -733,15 +742,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99FC5442-6448-E04F-A77B-2FCED9BD29CA}">
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="23" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23" style="12" customWidth="1"/>
-    <col min="5" max="5" width="23" style="13" customWidth="1"/>
-    <col min="6" max="7" width="23" style="12" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" style="11" customWidth="1"/>
+    <col min="5" max="5" width="23" style="12" customWidth="1"/>
+    <col min="6" max="6" width="23" style="11" customWidth="1"/>
+    <col min="7" max="7" width="23" style="16" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -763,7 +773,7 @@
       <c r="F1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="10" t="s">
@@ -774,22 +784,38 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="7"/>
+      <c r="A2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3">
+        <v>4199</v>
+      </c>
+      <c r="C2" s="3">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5">
+        <v>45572.666666666664</v>
+      </c>
+      <c r="E2" s="6">
+        <v>45572.6875</v>
+      </c>
+      <c r="F2" s="5">
+        <v>45572.673611111109</v>
+      </c>
+      <c r="G2" s="15">
+        <v>45579.583333333336</v>
+      </c>
+      <c r="H2" s="6">
+        <v>45579.57916666667</v>
+      </c>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3">
-        <v>4199</v>
+        <v>4323</v>
       </c>
       <c r="C3" s="3">
         <v>10</v>
@@ -803,7 +829,7 @@
       <c r="F3" s="5">
         <v>45572.673611111109</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="15">
         <v>45579.583333333336</v>
       </c>
       <c r="H3" s="6">
@@ -813,10 +839,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3">
-        <v>4323</v>
+        <v>4218</v>
       </c>
       <c r="C4" s="3">
         <v>10</v>
@@ -830,7 +856,7 @@
       <c r="F4" s="5">
         <v>45572.673611111109</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="15">
         <v>45579.583333333336</v>
       </c>
       <c r="H4" s="6">
@@ -840,48 +866,64 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3">
-        <v>4218</v>
+        <v>3937</v>
       </c>
       <c r="C5" s="3">
         <v>10</v>
       </c>
       <c r="D5" s="5">
-        <v>45572.666666666664</v>
+        <v>45572.618055555555</v>
       </c>
       <c r="E5" s="6">
-        <v>45572.6875</v>
+        <v>45572.652777777781</v>
       </c>
       <c r="F5" s="5">
-        <v>45572.673611111109</v>
-      </c>
-      <c r="G5" s="5">
-        <v>45579.583333333336</v>
+        <v>45572.630555555559</v>
+      </c>
+      <c r="G5" s="15">
+        <v>45579.576388888891</v>
       </c>
       <c r="H5" s="6">
-        <v>45579.57916666667</v>
+        <v>45579.572916666664</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="7"/>
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3">
+        <v>4039</v>
+      </c>
+      <c r="C6" s="3">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5">
+        <v>45572.618055555555</v>
+      </c>
+      <c r="E6" s="6">
+        <v>45572.652777777781</v>
+      </c>
+      <c r="F6" s="5">
+        <v>45572.630555555559</v>
+      </c>
+      <c r="G6" s="15">
+        <v>45579.576388888891</v>
+      </c>
+      <c r="H6" s="6">
+        <v>45579.572916666664</v>
+      </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3">
-        <v>3937</v>
+        <v>3954</v>
       </c>
       <c r="C7" s="3">
         <v>10</v>
@@ -895,7 +937,7 @@
       <c r="F7" s="5">
         <v>45572.630555555559</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="15">
         <v>45579.576388888891</v>
       </c>
       <c r="H7" s="6">
@@ -905,340 +947,412 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3">
-        <v>4039</v>
+        <v>4199</v>
       </c>
       <c r="C8" s="3">
         <v>10</v>
       </c>
       <c r="D8" s="5">
-        <v>45572.618055555555</v>
+        <v>45579.576388888891</v>
       </c>
       <c r="E8" s="6">
-        <v>45572.652777777781</v>
+        <v>45579.588194444441</v>
       </c>
       <c r="F8" s="5">
-        <v>45572.630555555559</v>
-      </c>
-      <c r="G8" s="5">
-        <v>45579.576388888891</v>
+        <v>45579.583333333336</v>
+      </c>
+      <c r="G8" s="15">
+        <v>45586.548611111109</v>
       </c>
       <c r="H8" s="6">
-        <v>45579.572916666664</v>
+        <v>45586.542361111111</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3">
-        <v>3954</v>
+        <v>4323</v>
       </c>
       <c r="C9" s="3">
         <v>10</v>
       </c>
       <c r="D9" s="5">
-        <v>45572.618055555555</v>
+        <v>45579.576388888891</v>
       </c>
       <c r="E9" s="6">
-        <v>45572.652777777781</v>
+        <v>45579.588194444441</v>
       </c>
       <c r="F9" s="5">
-        <v>45572.630555555559</v>
-      </c>
-      <c r="G9" s="5">
+        <v>45579.583333333336</v>
+      </c>
+      <c r="G9" s="15">
+        <v>45586.548611111109</v>
+      </c>
+      <c r="H9" s="6">
+        <v>45586.542361111111</v>
+      </c>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="3">
+        <v>4218</v>
+      </c>
+      <c r="C10" s="3">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5">
         <v>45579.576388888891</v>
       </c>
-      <c r="H9" s="6">
-        <v>45579.572916666664</v>
-      </c>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="7"/>
+      <c r="E10" s="6">
+        <v>45579.588194444441</v>
+      </c>
+      <c r="F10" s="5">
+        <v>45579.583333333336</v>
+      </c>
+      <c r="G10" s="15">
+        <v>45586.548611111109</v>
+      </c>
+      <c r="H10" s="6">
+        <v>45586.542361111111</v>
+      </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3">
-        <v>4199</v>
+        <v>3937</v>
       </c>
       <c r="C11" s="3">
         <v>10</v>
       </c>
       <c r="D11" s="5">
-        <v>45579.576388888891</v>
+        <v>45579.560416666667</v>
       </c>
       <c r="E11" s="6">
-        <v>45579.588194444441</v>
+        <v>45579.574305555558</v>
       </c>
       <c r="F11" s="5">
-        <v>45579.583333333336</v>
-      </c>
-      <c r="G11" s="5">
-        <v>45586.548611111109</v>
+        <v>45579.567361111112</v>
+      </c>
+      <c r="G11" s="15">
+        <v>45586.554861111108</v>
       </c>
       <c r="H11" s="6">
-        <v>45586.542361111111</v>
+        <v>45586.54791666667</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3">
-        <v>4323</v>
+        <v>4039</v>
       </c>
       <c r="C12" s="3">
         <v>10</v>
       </c>
       <c r="D12" s="5">
-        <v>45579.576388888891</v>
+        <v>45579.560416666667</v>
       </c>
       <c r="E12" s="6">
-        <v>45579.588194444441</v>
+        <v>45579.574305555558</v>
       </c>
       <c r="F12" s="5">
-        <v>45579.583333333336</v>
-      </c>
-      <c r="G12" s="5">
-        <v>45586.548611111109</v>
+        <v>45579.567361111112</v>
+      </c>
+      <c r="G12" s="15">
+        <v>45586.554861111108</v>
       </c>
       <c r="H12" s="6">
-        <v>45586.542361111111</v>
+        <v>45586.54791666667</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3">
-        <v>4218</v>
+        <v>3954</v>
       </c>
       <c r="C13" s="3">
         <v>10</v>
       </c>
       <c r="D13" s="5">
-        <v>45579.576388888891</v>
+        <v>45579.560416666667</v>
       </c>
       <c r="E13" s="6">
-        <v>45579.588194444441</v>
+        <v>45579.574305555558</v>
       </c>
       <c r="F13" s="5">
-        <v>45579.583333333336</v>
-      </c>
-      <c r="G13" s="5">
-        <v>45586.548611111109</v>
+        <v>45579.567361111112</v>
+      </c>
+      <c r="G13" s="15">
+        <v>45586.554861111108</v>
       </c>
       <c r="H13" s="6">
-        <v>45586.542361111111</v>
+        <v>45586.54791666667</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="7"/>
+      <c r="A14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="3">
+        <v>4199</v>
+      </c>
+      <c r="C14" s="3">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5">
+        <v>45586.53125</v>
+      </c>
+      <c r="E14" s="6">
+        <v>45586.543055555558</v>
+      </c>
+      <c r="F14" s="5">
+        <v>45586.534722222219</v>
+      </c>
+      <c r="G14" s="15">
+        <v>45593.798611111109</v>
+      </c>
+      <c r="H14" s="6">
+        <v>45593.79583333333</v>
+      </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B15" s="3">
-        <v>3937</v>
+        <v>4323</v>
       </c>
       <c r="C15" s="3">
         <v>10</v>
       </c>
       <c r="D15" s="5">
-        <v>45579.560416666667</v>
+        <v>45586.53125</v>
       </c>
       <c r="E15" s="6">
-        <v>45579.574305555558</v>
+        <v>45586.543055555558</v>
       </c>
       <c r="F15" s="5">
-        <v>45579.567361111112</v>
-      </c>
-      <c r="G15" s="5">
-        <v>45586.554861111108</v>
+        <v>45586.534722222219</v>
+      </c>
+      <c r="G15" s="15">
+        <v>45593.798611111109</v>
       </c>
       <c r="H15" s="6">
-        <v>45586.54791666667</v>
+        <v>45593.79583333333</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B16" s="3">
-        <v>4039</v>
+        <v>4218</v>
       </c>
       <c r="C16" s="3">
         <v>10</v>
       </c>
       <c r="D16" s="5">
-        <v>45579.560416666667</v>
+        <v>45586.53125</v>
       </c>
       <c r="E16" s="6">
-        <v>45579.574305555558</v>
+        <v>45586.543055555558</v>
       </c>
       <c r="F16" s="5">
-        <v>45579.567361111112</v>
-      </c>
-      <c r="G16" s="5">
-        <v>45586.554861111108</v>
+        <v>45586.534722222219</v>
+      </c>
+      <c r="G16" s="15">
+        <v>45593.798611111109</v>
       </c>
       <c r="H16" s="6">
-        <v>45586.54791666667</v>
+        <v>45593.79583333333</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3">
-        <v>3954</v>
+        <v>3937</v>
       </c>
       <c r="C17" s="3">
         <v>10</v>
       </c>
       <c r="D17" s="5">
-        <v>45579.560416666667</v>
+        <v>45586.548611111109</v>
       </c>
       <c r="E17" s="6">
-        <v>45579.574305555558</v>
+        <v>45586.558333333334</v>
       </c>
       <c r="F17" s="5">
-        <v>45579.567361111112</v>
-      </c>
-      <c r="G17" s="5">
-        <v>45586.554861111108</v>
+        <v>45586.551388888889</v>
+      </c>
+      <c r="G17" s="15">
+        <v>45593.84375</v>
       </c>
       <c r="H17" s="6">
-        <v>45586.54791666667</v>
+        <v>45593.840277777781</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="F18" s="8"/>
+      <c r="A18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4039</v>
+      </c>
+      <c r="C18" s="3">
+        <v>10</v>
+      </c>
+      <c r="D18" s="5">
+        <v>45586.548611111109</v>
+      </c>
+      <c r="E18" s="6">
+        <v>45586.558333333334</v>
+      </c>
+      <c r="F18" s="5">
+        <v>45586.551388888889</v>
+      </c>
+      <c r="G18" s="15">
+        <v>45593.84375</v>
+      </c>
+      <c r="H18" s="6">
+        <v>45593.840277777781</v>
+      </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B19" s="3">
-        <v>4199</v>
+        <v>3954</v>
       </c>
       <c r="C19" s="3">
         <v>10</v>
       </c>
       <c r="D19" s="5">
-        <v>45586.53125</v>
+        <v>45586.548611111109</v>
       </c>
       <c r="E19" s="6">
-        <v>45586.543055555558</v>
+        <v>45586.558333333334</v>
       </c>
       <c r="F19" s="5">
-        <v>45586.534722222219</v>
-      </c>
-      <c r="G19" s="5">
-        <v>45593.798611111109</v>
+        <v>45586.551388888889</v>
+      </c>
+      <c r="G19" s="15">
+        <v>45593.84375</v>
       </c>
       <c r="H19" s="6">
-        <v>45593.79583333333</v>
+        <v>45593.840277777781</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B20" s="3">
-        <v>4323</v>
+        <v>4199</v>
       </c>
       <c r="C20" s="3">
         <v>10</v>
       </c>
       <c r="D20" s="5">
-        <v>45586.53125</v>
+        <v>45599.890277777777</v>
       </c>
       <c r="E20" s="6">
-        <v>45586.543055555558</v>
+        <v>45599.904166666667</v>
       </c>
       <c r="F20" s="5">
-        <v>45586.534722222219</v>
-      </c>
-      <c r="G20" s="5">
-        <v>45593.798611111109</v>
+        <v>45599.897222222222</v>
+      </c>
+      <c r="G20" s="15">
+        <v>45607.413194444445</v>
       </c>
       <c r="H20" s="6">
-        <v>45593.79583333333</v>
+        <v>45607.409722222219</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3">
+        <v>4323</v>
+      </c>
+      <c r="C21" s="3">
+        <v>10</v>
+      </c>
+      <c r="D21" s="5">
+        <v>45599.890277777777</v>
+      </c>
+      <c r="E21" s="6">
+        <v>45599.904166666667</v>
+      </c>
+      <c r="F21" s="5">
+        <v>45599.897222222222</v>
+      </c>
+      <c r="G21" s="15">
+        <v>45607.413194444445</v>
+      </c>
+      <c r="H21" s="6">
+        <v>45607.409722222219</v>
+      </c>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="3">
         <v>4218</v>
       </c>
-      <c r="C21" s="3">
-        <v>10</v>
-      </c>
-      <c r="D21" s="5">
-        <v>45586.53125</v>
-      </c>
-      <c r="E21" s="6">
-        <v>45586.543055555558</v>
-      </c>
-      <c r="F21" s="5">
-        <v>45586.534722222219</v>
-      </c>
-      <c r="G21" s="5">
-        <v>45593.798611111109</v>
-      </c>
-      <c r="H21" s="6">
-        <v>45593.79583333333</v>
-      </c>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="3">
+        <v>10</v>
+      </c>
+      <c r="D22" s="5">
+        <v>45599.890277777777</v>
+      </c>
+      <c r="E22" s="6">
+        <v>45599.904166666667</v>
+      </c>
+      <c r="F22" s="5">
+        <v>45599.897222222222</v>
+      </c>
+      <c r="G22" s="15">
+        <v>45607.413194444445</v>
+      </c>
+      <c r="H22" s="6">
+        <v>45607.409722222219</v>
+      </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B23" s="3">
         <v>3937</v>
@@ -1247,25 +1361,27 @@
         <v>10</v>
       </c>
       <c r="D23" s="5">
-        <v>45586.548611111109</v>
+        <v>45599.805555555555</v>
       </c>
       <c r="E23" s="6">
-        <v>45586.558333333334</v>
+        <v>45599.81527777778</v>
       </c>
       <c r="F23" s="5">
-        <v>45586.551388888889</v>
-      </c>
-      <c r="G23" s="5">
-        <v>45593.84375</v>
+        <v>45599.808333333334</v>
+      </c>
+      <c r="G23" s="15">
+        <v>45604.482638888891</v>
       </c>
       <c r="H23" s="6">
-        <v>45593.840277777781</v>
-      </c>
-      <c r="I23" s="4"/>
+        <v>45604.478472222225</v>
+      </c>
+      <c r="I23" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B24" s="3">
         <v>4039</v>
@@ -1274,25 +1390,25 @@
         <v>10</v>
       </c>
       <c r="D24" s="5">
-        <v>45586.548611111109</v>
+        <v>45599.805555555555</v>
       </c>
       <c r="E24" s="6">
-        <v>45586.558333333334</v>
+        <v>45599.81527777778</v>
       </c>
       <c r="F24" s="5">
-        <v>45586.551388888889</v>
-      </c>
-      <c r="G24" s="5">
-        <v>45593.84375</v>
+        <v>45599.808333333334</v>
+      </c>
+      <c r="G24" s="15">
+        <v>45604.482638888891</v>
       </c>
       <c r="H24" s="6">
-        <v>45593.840277777781</v>
+        <v>45604.478472222225</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3">
         <v>3954</v>
@@ -1301,1474 +1417,1223 @@
         <v>10</v>
       </c>
       <c r="D25" s="5">
-        <v>45586.548611111109</v>
+        <v>45599.805555555555</v>
       </c>
       <c r="E25" s="6">
-        <v>45586.558333333334</v>
+        <v>45599.81527777778</v>
       </c>
       <c r="F25" s="5">
-        <v>45586.551388888889</v>
-      </c>
-      <c r="G25" s="5">
-        <v>45593.84375</v>
+        <v>45599.808333333334</v>
+      </c>
+      <c r="G25" s="15">
+        <v>45604.482638888891</v>
       </c>
       <c r="H25" s="6">
-        <v>45593.840277777781</v>
+        <v>45604.478472222225</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4199</v>
+      </c>
+      <c r="C26" s="3">
+        <v>10</v>
+      </c>
+      <c r="D26" s="5">
+        <v>45607.576388888891</v>
+      </c>
+      <c r="E26" s="6">
+        <v>45607.584027777775</v>
+      </c>
+      <c r="F26" s="5">
+        <v>45607.579861111109</v>
+      </c>
+      <c r="G26" s="15">
+        <v>45614.552083333336</v>
+      </c>
+      <c r="H26" s="6">
+        <v>45614.549305555556</v>
+      </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B27" s="3">
-        <v>4199</v>
+        <v>4323</v>
       </c>
       <c r="C27" s="3">
         <v>10</v>
       </c>
       <c r="D27" s="5">
-        <v>45599.890277777777</v>
+        <v>45607.576388888891</v>
       </c>
       <c r="E27" s="6">
-        <v>45599.904166666667</v>
+        <v>45607.584027777775</v>
       </c>
       <c r="F27" s="5">
-        <v>45599.897222222222</v>
-      </c>
-      <c r="G27" s="5">
-        <v>45607.413194444445</v>
+        <v>45607.579861111109</v>
+      </c>
+      <c r="G27" s="15">
+        <v>45614.552083333336</v>
       </c>
       <c r="H27" s="6">
-        <v>45607.409722222219</v>
+        <v>45614.549305555556</v>
       </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B28" s="3">
-        <v>4323</v>
+        <v>4218</v>
       </c>
       <c r="C28" s="3">
         <v>10</v>
       </c>
       <c r="D28" s="5">
-        <v>45599.890277777777</v>
+        <v>45607.576388888891</v>
       </c>
       <c r="E28" s="6">
-        <v>45599.904166666667</v>
+        <v>45607.584027777775</v>
       </c>
       <c r="F28" s="5">
-        <v>45599.897222222222</v>
-      </c>
-      <c r="G28" s="5">
-        <v>45607.413194444445</v>
+        <v>45607.579861111109</v>
+      </c>
+      <c r="G28" s="15">
+        <v>45614.552083333336</v>
       </c>
       <c r="H28" s="6">
-        <v>45607.409722222219</v>
+        <v>45614.549305555556</v>
       </c>
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B29" s="3">
-        <v>4218</v>
+        <v>4199</v>
       </c>
       <c r="C29" s="3">
         <v>10</v>
       </c>
       <c r="D29" s="5">
-        <v>45599.890277777777</v>
+        <v>45628.51666666667</v>
       </c>
       <c r="E29" s="6">
-        <v>45599.904166666667</v>
+        <v>45628.523611111108</v>
       </c>
       <c r="F29" s="5">
-        <v>45599.897222222222</v>
-      </c>
-      <c r="G29" s="5">
-        <v>45607.413194444445</v>
+        <v>45628.518750000003</v>
+      </c>
+      <c r="G29" s="15">
+        <v>45635.59375</v>
       </c>
       <c r="H29" s="6">
-        <v>45607.409722222219</v>
+        <v>45635.591666666667</v>
       </c>
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+      <c r="A30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="3">
+        <v>4323</v>
+      </c>
+      <c r="C30" s="3">
+        <v>10</v>
+      </c>
+      <c r="D30" s="5">
+        <v>45628.51666666667</v>
+      </c>
+      <c r="E30" s="6">
+        <v>45628.523611111108</v>
+      </c>
+      <c r="F30" s="5">
+        <v>45628.518750000003</v>
+      </c>
+      <c r="G30" s="15">
+        <v>45635.59375</v>
+      </c>
+      <c r="H30" s="6">
+        <v>45635.591666666667</v>
+      </c>
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B31" s="3">
-        <v>3937</v>
+        <v>4218</v>
       </c>
       <c r="C31" s="3">
         <v>10</v>
       </c>
       <c r="D31" s="5">
-        <v>45599.805555555555</v>
+        <v>45628.51666666667</v>
       </c>
       <c r="E31" s="6">
-        <v>45599.81527777778</v>
+        <v>45628.523611111108</v>
       </c>
       <c r="F31" s="5">
-        <v>45599.808333333334</v>
-      </c>
-      <c r="G31" s="5">
-        <v>45604.482638888891</v>
+        <v>45628.518750000003</v>
+      </c>
+      <c r="G31" s="15">
+        <v>45635.59375</v>
       </c>
       <c r="H31" s="6">
-        <v>45604.478472222225</v>
-      </c>
-      <c r="I31" t="s">
-        <v>10</v>
-      </c>
+        <v>45635.591666666667</v>
+      </c>
+      <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B32" s="3">
-        <v>4039</v>
+        <v>4199</v>
       </c>
       <c r="C32" s="3">
         <v>10</v>
       </c>
       <c r="D32" s="5">
-        <v>45599.805555555555</v>
+        <v>45614.560416666667</v>
       </c>
       <c r="E32" s="6">
-        <v>45599.81527777778</v>
+        <v>45614.574305555558</v>
       </c>
       <c r="F32" s="5">
-        <v>45599.808333333334</v>
-      </c>
-      <c r="G32" s="5">
-        <v>45604.482638888891</v>
+        <v>45614.5625</v>
+      </c>
+      <c r="G32" s="15">
+        <v>45621.524305555555</v>
       </c>
       <c r="H32" s="6">
-        <v>45604.478472222225</v>
+        <v>45621.521527777775</v>
       </c>
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B33" s="3">
-        <v>3954</v>
+        <v>4323</v>
       </c>
       <c r="C33" s="3">
         <v>10</v>
       </c>
       <c r="D33" s="5">
-        <v>45599.805555555555</v>
+        <v>45614.560416666667</v>
       </c>
       <c r="E33" s="6">
-        <v>45599.81527777778</v>
+        <v>45614.574305555558</v>
       </c>
       <c r="F33" s="5">
-        <v>45599.808333333334</v>
-      </c>
-      <c r="G33" s="5">
-        <v>45604.482638888891</v>
+        <v>45614.5625</v>
+      </c>
+      <c r="G33" s="15">
+        <v>45621.524305555555</v>
       </c>
       <c r="H33" s="6">
-        <v>45604.478472222225</v>
+        <v>45621.521527777775</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="8"/>
+      <c r="A34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="3">
+        <v>4218</v>
+      </c>
+      <c r="C34" s="3">
+        <v>10</v>
+      </c>
+      <c r="D34" s="5">
+        <v>45614.560416666667</v>
+      </c>
+      <c r="E34" s="6">
+        <v>45614.574305555558</v>
+      </c>
+      <c r="F34" s="5">
+        <v>45614.5625</v>
+      </c>
+      <c r="G34" s="15">
+        <v>45621.524305555555</v>
+      </c>
+      <c r="H34" s="6">
+        <v>45621.521527777775</v>
+      </c>
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B35" s="3">
-        <v>4199</v>
-      </c>
-      <c r="C35" s="3">
-        <v>10</v>
+        <v>3910</v>
+      </c>
+      <c r="C35" s="13">
+        <v>60</v>
       </c>
       <c r="D35" s="5">
-        <v>45607.576388888891</v>
+        <v>45614.555555555555</v>
       </c>
       <c r="E35" s="6">
-        <v>45607.584027777775</v>
+        <v>45615.334027777775</v>
       </c>
       <c r="F35" s="5">
-        <v>45607.579861111109</v>
-      </c>
-      <c r="G35" s="5">
-        <v>45614.552083333336</v>
+        <v>45614.559027777781</v>
+      </c>
+      <c r="G35" s="15">
+        <v>45621.388888888891</v>
       </c>
       <c r="H35" s="6">
-        <v>45614.549305555556</v>
-      </c>
-      <c r="I35" s="4"/>
+        <v>45621.386805555558</v>
+      </c>
+      <c r="I35" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3">
-        <v>4323</v>
+        <v>4039</v>
       </c>
       <c r="C36" s="3">
         <v>10</v>
       </c>
       <c r="D36" s="5">
-        <v>45607.576388888891</v>
+        <v>45614.555555555555</v>
       </c>
       <c r="E36" s="6">
-        <v>45607.584027777775</v>
+        <v>45615.334027777775</v>
       </c>
       <c r="F36" s="5">
-        <v>45607.579861111109</v>
-      </c>
-      <c r="G36" s="5">
-        <v>45614.552083333336</v>
+        <v>45614.559027777781</v>
+      </c>
+      <c r="G36" s="15">
+        <v>45621.388888888891</v>
       </c>
       <c r="H36" s="6">
-        <v>45614.549305555556</v>
+        <v>45621.386805555558</v>
       </c>
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B37" s="3">
-        <v>4218</v>
+        <v>3954</v>
       </c>
       <c r="C37" s="3">
         <v>10</v>
       </c>
       <c r="D37" s="5">
-        <v>45607.576388888891</v>
+        <v>45614.555555555555</v>
       </c>
       <c r="E37" s="6">
-        <v>45607.584027777775</v>
+        <v>45615.334027777775</v>
       </c>
       <c r="F37" s="5">
-        <v>45607.579861111109</v>
-      </c>
-      <c r="G37" s="5">
-        <v>45614.552083333336</v>
+        <v>45614.559027777781</v>
+      </c>
+      <c r="G37" s="15">
+        <v>45621.388888888891</v>
       </c>
       <c r="H37" s="6">
-        <v>45614.549305555556</v>
+        <v>45621.386805555558</v>
       </c>
       <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="8"/>
+      <c r="A38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="3">
+        <v>4199</v>
+      </c>
+      <c r="C38" s="3">
+        <v>10</v>
+      </c>
+      <c r="D38" s="5">
+        <v>45621.576388888891</v>
+      </c>
+      <c r="E38" s="6">
+        <v>45621.584027777775</v>
+      </c>
+      <c r="F38" s="5">
+        <v>45621.578472222223</v>
+      </c>
+      <c r="G38" s="15">
+        <v>45628.504166666666</v>
+      </c>
+      <c r="H38" s="6">
+        <v>45628.502083333333</v>
+      </c>
       <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B39" s="3">
-        <v>4199</v>
+        <v>4323</v>
       </c>
       <c r="C39" s="3">
         <v>10</v>
       </c>
       <c r="D39" s="5">
-        <v>45628.51666666667</v>
+        <v>45621.576388888891</v>
       </c>
       <c r="E39" s="6">
-        <v>45628.523611111108</v>
+        <v>45621.584027777775</v>
       </c>
       <c r="F39" s="5">
-        <v>45628.518750000003</v>
-      </c>
-      <c r="G39" s="5">
-        <v>45635.59375</v>
+        <v>45621.578472222223</v>
+      </c>
+      <c r="G39" s="15">
+        <v>45628.504166666666</v>
       </c>
       <c r="H39" s="6">
-        <v>45635.591666666667</v>
+        <v>45628.502083333333</v>
       </c>
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B40" s="3">
-        <v>4323</v>
+        <v>4103</v>
       </c>
       <c r="C40" s="3">
         <v>10</v>
       </c>
       <c r="D40" s="5">
-        <v>45628.51666666667</v>
+        <v>45621.576388888891</v>
       </c>
       <c r="E40" s="6">
-        <v>45628.523611111108</v>
+        <v>45621.584027777775</v>
       </c>
       <c r="F40" s="5">
-        <v>45628.518750000003</v>
-      </c>
-      <c r="G40" s="5">
-        <v>45635.59375</v>
+        <v>45621.578472222223</v>
+      </c>
+      <c r="G40" s="15">
+        <v>45628.504166666666</v>
       </c>
       <c r="H40" s="6">
-        <v>45635.591666666667</v>
+        <v>45628.502083333333</v>
       </c>
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3">
-        <v>4218</v>
+        <v>3982</v>
       </c>
       <c r="C41" s="3">
         <v>10</v>
       </c>
       <c r="D41" s="5">
-        <v>45628.51666666667</v>
+        <v>45621.55972222222</v>
       </c>
       <c r="E41" s="6">
-        <v>45628.523611111108</v>
+        <v>45621.566666666666</v>
       </c>
       <c r="F41" s="5">
-        <v>45628.518750000003</v>
-      </c>
-      <c r="G41" s="5">
-        <v>45635.59375</v>
+        <v>45621.5625</v>
+      </c>
+      <c r="G41" s="15">
+        <v>45628.541666666664</v>
       </c>
       <c r="H41" s="6">
-        <v>45635.591666666667</v>
+        <v>45628.539583333331</v>
       </c>
       <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="8"/>
+      <c r="A42" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" s="3">
+        <v>4039</v>
+      </c>
+      <c r="C42" s="3">
+        <v>10</v>
+      </c>
+      <c r="D42" s="5">
+        <v>45621.55972222222</v>
+      </c>
+      <c r="E42" s="6">
+        <v>45621.566666666666</v>
+      </c>
+      <c r="F42" s="5">
+        <v>45621.5625</v>
+      </c>
+      <c r="G42" s="15">
+        <v>45628.541666666664</v>
+      </c>
+      <c r="H42" s="6">
+        <v>45628.539583333331</v>
+      </c>
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B43" s="3">
-        <v>4199</v>
+        <v>3954</v>
       </c>
       <c r="C43" s="3">
         <v>10</v>
       </c>
       <c r="D43" s="5">
-        <v>45614.560416666667</v>
+        <v>45621.55972222222</v>
       </c>
       <c r="E43" s="6">
-        <v>45614.574305555558</v>
+        <v>45621.566666666666</v>
       </c>
       <c r="F43" s="5">
-        <v>45614.5625</v>
-      </c>
-      <c r="G43" s="5">
-        <v>45621.524305555555</v>
+        <v>45621.5625</v>
+      </c>
+      <c r="G43" s="15">
+        <v>45628.541666666664</v>
       </c>
       <c r="H43" s="6">
-        <v>45621.521527777775</v>
+        <v>45628.539583333331</v>
       </c>
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B44" s="3">
-        <v>4323</v>
+        <v>3982</v>
       </c>
       <c r="C44" s="3">
         <v>10</v>
       </c>
       <c r="D44" s="5">
-        <v>45614.560416666667</v>
+        <v>45628.544444444444</v>
       </c>
       <c r="E44" s="6">
-        <v>45614.574305555558</v>
+        <v>45628.551388888889</v>
       </c>
       <c r="F44" s="5">
-        <v>45614.5625</v>
-      </c>
-      <c r="G44" s="5">
-        <v>45621.524305555555</v>
+        <v>45628.54583333333</v>
+      </c>
+      <c r="G44" s="15">
+        <v>45635.529166666667</v>
       </c>
       <c r="H44" s="6">
-        <v>45621.521527777775</v>
+        <v>45635.526388888888</v>
       </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B45" s="3">
-        <v>4218</v>
+        <v>4039</v>
       </c>
       <c r="C45" s="3">
         <v>10</v>
       </c>
       <c r="D45" s="5">
-        <v>45614.560416666667</v>
+        <v>45628.544444444444</v>
       </c>
       <c r="E45" s="6">
-        <v>45614.574305555558</v>
+        <v>45628.551388888889</v>
       </c>
       <c r="F45" s="5">
-        <v>45614.5625</v>
-      </c>
-      <c r="G45" s="5">
-        <v>45621.524305555555</v>
+        <v>45628.54583333333</v>
+      </c>
+      <c r="G45" s="15">
+        <v>45635.529166666667</v>
       </c>
       <c r="H45" s="6">
-        <v>45621.521527777775</v>
+        <v>45635.526388888888</v>
       </c>
       <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="8"/>
+      <c r="A46" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="3">
+        <v>3954</v>
+      </c>
+      <c r="C46" s="3">
+        <v>10</v>
+      </c>
+      <c r="D46" s="5">
+        <v>45628.544444444444</v>
+      </c>
+      <c r="E46" s="6">
+        <v>45628.551388888889</v>
+      </c>
+      <c r="F46" s="5">
+        <v>45628.54583333333</v>
+      </c>
+      <c r="G46" s="15">
+        <v>45635.529166666667</v>
+      </c>
+      <c r="H46" s="6">
+        <v>45635.526388888888</v>
+      </c>
       <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B47" s="3">
-        <v>3910</v>
-      </c>
-      <c r="C47" s="14">
-        <v>60</v>
+        <v>4199</v>
+      </c>
+      <c r="C47" s="3">
+        <v>10</v>
       </c>
       <c r="D47" s="5">
-        <v>45614.555555555555</v>
+        <v>45635.593055555553</v>
       </c>
       <c r="E47" s="6">
-        <v>45615.334027777775</v>
+        <v>45635.6</v>
       </c>
       <c r="F47" s="5">
-        <v>45614.559027777781</v>
-      </c>
-      <c r="G47" s="5">
-        <v>45621.388888888891</v>
+        <v>45635.595138888886</v>
+      </c>
+      <c r="G47" s="15">
+        <v>45642.524305555555</v>
       </c>
       <c r="H47" s="6">
-        <v>45621.386805555558</v>
-      </c>
-      <c r="I47" t="s">
-        <v>9</v>
+        <v>45642.520833333336</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B48" s="3">
-        <v>4039</v>
+        <v>4323</v>
       </c>
       <c r="C48" s="3">
         <v>10</v>
       </c>
       <c r="D48" s="5">
-        <v>45614.555555555555</v>
+        <v>45635.593055555553</v>
       </c>
       <c r="E48" s="6">
-        <v>45615.334027777775</v>
+        <v>45635.6</v>
       </c>
       <c r="F48" s="5">
-        <v>45614.559027777781</v>
-      </c>
-      <c r="G48" s="5">
-        <v>45621.388888888891</v>
+        <v>45635.595138888886</v>
+      </c>
+      <c r="G48" s="15">
+        <v>45642.524305555555</v>
       </c>
       <c r="H48" s="6">
-        <v>45621.386805555558</v>
-      </c>
-      <c r="I48" s="4"/>
+        <v>45642.520833333336</v>
+      </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B49" s="3">
-        <v>3954</v>
+        <v>4218</v>
       </c>
       <c r="C49" s="3">
         <v>10</v>
       </c>
       <c r="D49" s="5">
-        <v>45614.555555555555</v>
+        <v>45635.593055555553</v>
       </c>
       <c r="E49" s="6">
-        <v>45615.334027777775</v>
+        <v>45635.6</v>
       </c>
       <c r="F49" s="5">
-        <v>45614.559027777781</v>
-      </c>
-      <c r="G49" s="5">
-        <v>45621.388888888891</v>
+        <v>45635.595138888886</v>
+      </c>
+      <c r="G49" s="15">
+        <v>45642.524305555555</v>
       </c>
       <c r="H49" s="6">
-        <v>45621.386805555558</v>
-      </c>
-      <c r="I49" s="4"/>
+        <v>45640.560416666667</v>
+      </c>
+      <c r="I49" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="8"/>
+      <c r="A50" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="3">
+        <v>3982</v>
+      </c>
+      <c r="C50" s="3">
+        <v>10</v>
+      </c>
+      <c r="D50" s="5">
+        <v>45635.534722222219</v>
+      </c>
+      <c r="E50" s="6">
+        <v>45635.542361111111</v>
+      </c>
+      <c r="F50" s="5">
+        <v>45635.536805555559</v>
+      </c>
+      <c r="G50" s="15">
+        <v>45642.538194444445</v>
+      </c>
+      <c r="H50" s="6">
+        <v>45642.535416666666</v>
+      </c>
       <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B51" s="3">
-        <v>4199</v>
+        <v>4039</v>
       </c>
       <c r="C51" s="3">
         <v>10</v>
       </c>
       <c r="D51" s="5">
-        <v>45621.576388888891</v>
+        <v>45635.534722222219</v>
       </c>
       <c r="E51" s="6">
-        <v>45621.584027777775</v>
+        <v>45635.542361111111</v>
       </c>
       <c r="F51" s="5">
-        <v>45621.578472222223</v>
-      </c>
-      <c r="G51" s="5">
-        <v>45628.504166666666</v>
+        <v>45635.536805555559</v>
+      </c>
+      <c r="G51" s="15">
+        <v>45642.538194444445</v>
       </c>
       <c r="H51" s="6">
-        <v>45628.502083333333</v>
+        <v>45642.535416666666</v>
       </c>
       <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B52" s="3">
-        <v>4323</v>
+        <v>3954</v>
       </c>
       <c r="C52" s="3">
         <v>10</v>
       </c>
       <c r="D52" s="5">
-        <v>45621.576388888891</v>
+        <v>45635.534722222219</v>
       </c>
       <c r="E52" s="6">
-        <v>45621.584027777775</v>
+        <v>45635.542361111111</v>
       </c>
       <c r="F52" s="5">
-        <v>45621.578472222223</v>
-      </c>
-      <c r="G52" s="5">
-        <v>45628.504166666666</v>
+        <v>45635.536805555559</v>
+      </c>
+      <c r="G52" s="15">
+        <v>45642.538194444445</v>
       </c>
       <c r="H52" s="6">
-        <v>45628.502083333333</v>
+        <v>45642.535416666666</v>
       </c>
       <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B53" s="3">
-        <v>4103</v>
+        <v>4199</v>
       </c>
       <c r="C53" s="3">
         <v>10</v>
       </c>
       <c r="D53" s="5">
-        <v>45621.576388888891</v>
+        <v>45677.460416666669</v>
       </c>
       <c r="E53" s="6">
-        <v>45621.584027777775</v>
+        <v>45677.467361111114</v>
       </c>
       <c r="F53" s="5">
-        <v>45621.578472222223</v>
-      </c>
-      <c r="G53" s="5">
-        <v>45628.504166666666</v>
+        <v>45677.461805555555</v>
+      </c>
+      <c r="G53" s="15">
+        <v>45684.579861111109</v>
       </c>
       <c r="H53" s="6">
-        <v>45628.502083333333</v>
+        <v>45684.578472222223</v>
       </c>
       <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="8"/>
+      <c r="A54" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="3">
+        <v>3954</v>
+      </c>
+      <c r="C54" s="3">
+        <v>10</v>
+      </c>
+      <c r="D54" s="5">
+        <v>45677.460416666669</v>
+      </c>
+      <c r="E54" s="6">
+        <v>45677.467361111114</v>
+      </c>
+      <c r="F54" s="5">
+        <v>45677.461805555555</v>
+      </c>
+      <c r="G54" s="15">
+        <v>45684.579861111109</v>
+      </c>
+      <c r="H54" s="6">
+        <v>45684.578472222223</v>
+      </c>
       <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B55" s="3">
-        <v>3982</v>
+        <v>5114</v>
       </c>
       <c r="C55" s="3">
         <v>10</v>
       </c>
       <c r="D55" s="5">
-        <v>45621.55972222222</v>
+        <v>45677.460416666669</v>
       </c>
       <c r="E55" s="6">
-        <v>45621.566666666666</v>
+        <v>45677.467361111114</v>
       </c>
       <c r="F55" s="5">
-        <v>45621.5625</v>
-      </c>
-      <c r="G55" s="14">
-        <v>45628.541666666664</v>
+        <v>45677.461805555555</v>
+      </c>
+      <c r="G55" s="15">
+        <v>45684.579861111109</v>
       </c>
       <c r="H55" s="6">
-        <v>45628.539583333331</v>
+        <v>45684.578472222223</v>
       </c>
       <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B56" s="3">
-        <v>4039</v>
+        <v>3082</v>
       </c>
       <c r="C56" s="3">
         <v>10</v>
       </c>
       <c r="D56" s="5">
-        <v>45621.55972222222</v>
+        <v>45677.473611111112</v>
       </c>
       <c r="E56" s="6">
-        <v>45621.566666666666</v>
+        <v>45677.480555555558</v>
       </c>
       <c r="F56" s="5">
-        <v>45621.5625</v>
-      </c>
-      <c r="G56" s="14">
-        <v>45628.541666666664</v>
+        <v>45677.475694444445</v>
+      </c>
+      <c r="G56" s="15">
+        <v>45684.40625</v>
       </c>
       <c r="H56" s="6">
-        <v>45628.539583333331</v>
+        <v>45684.404166666667</v>
       </c>
       <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B57" s="3">
-        <v>3954</v>
+        <v>4039</v>
       </c>
       <c r="C57" s="3">
         <v>10</v>
       </c>
       <c r="D57" s="5">
-        <v>45621.55972222222</v>
+        <v>45677.473611111112</v>
       </c>
       <c r="E57" s="6">
-        <v>45621.566666666666</v>
+        <v>45677.480555555558</v>
       </c>
       <c r="F57" s="5">
-        <v>45621.5625</v>
-      </c>
-      <c r="G57" s="14">
-        <v>45628.541666666664</v>
+        <v>45677.475694444445</v>
+      </c>
+      <c r="G57" s="15">
+        <v>45684.40625</v>
       </c>
       <c r="H57" s="6">
-        <v>45628.539583333331</v>
+        <v>45684.404166666667</v>
       </c>
       <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
+      <c r="A58" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="3">
+        <v>5198</v>
+      </c>
+      <c r="C58" s="3">
+        <v>10</v>
+      </c>
       <c r="D58" s="8"/>
-      <c r="I58" s="4"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8"/>
+      <c r="H58" s="7"/>
+      <c r="I58" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B59" s="3">
-        <v>3982</v>
+        <v>4199</v>
       </c>
       <c r="C59" s="3">
         <v>10</v>
       </c>
       <c r="D59" s="5">
-        <v>45628.544444444444</v>
+        <v>45684.568055555559</v>
       </c>
       <c r="E59" s="6">
-        <v>45628.551388888889</v>
+        <v>45684.581944444442</v>
       </c>
       <c r="F59" s="5">
-        <v>45628.54583333333</v>
-      </c>
-      <c r="G59" s="5">
-        <v>45635.529166666667</v>
+        <v>45684.572916666664</v>
+      </c>
+      <c r="G59" s="15">
+        <v>45691.548611111109</v>
       </c>
       <c r="H59" s="6">
-        <v>45635.526388888888</v>
+        <v>45691.546527777777</v>
       </c>
       <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B60" s="3">
-        <v>4039</v>
+        <v>3954</v>
       </c>
       <c r="C60" s="3">
         <v>10</v>
       </c>
       <c r="D60" s="5">
-        <v>45628.544444444444</v>
+        <v>45684.568055555559</v>
       </c>
       <c r="E60" s="6">
-        <v>45628.551388888889</v>
+        <v>45684.581944444442</v>
       </c>
       <c r="F60" s="5">
-        <v>45628.54583333333</v>
-      </c>
-      <c r="G60" s="5">
-        <v>45635.529166666667</v>
+        <v>45684.572916666664</v>
+      </c>
+      <c r="G60" s="15">
+        <v>45691.548611111109</v>
       </c>
       <c r="H60" s="6">
-        <v>45635.526388888888</v>
+        <v>45691.546527777777</v>
       </c>
       <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B61" s="3">
-        <v>3954</v>
+        <v>5114</v>
       </c>
       <c r="C61" s="3">
         <v>10</v>
       </c>
-      <c r="D61" s="5">
-        <v>45628.544444444444</v>
-      </c>
-      <c r="E61" s="6">
-        <v>45628.551388888889</v>
-      </c>
-      <c r="F61" s="5">
-        <v>45628.54583333333</v>
-      </c>
-      <c r="G61" s="5">
-        <v>45635.529166666667</v>
-      </c>
-      <c r="H61" s="6">
-        <v>45635.526388888888</v>
-      </c>
-      <c r="I61" s="4"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8"/>
+      <c r="H61" s="7"/>
+      <c r="I61" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C62" s="3"/>
+      <c r="A62" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="3">
+        <v>3982</v>
+      </c>
+      <c r="C62" s="3">
+        <v>10</v>
+      </c>
+      <c r="D62" s="5">
+        <v>45684.560416666667</v>
+      </c>
+      <c r="E62" s="6">
+        <v>45684.567361111112</v>
+      </c>
+      <c r="F62" s="5">
+        <v>45684.5625</v>
+      </c>
+      <c r="G62" s="15">
+        <v>45691.40625</v>
+      </c>
+      <c r="H62" s="6">
+        <v>45691.404166666667</v>
+      </c>
+      <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="B63" s="3">
-        <v>4199</v>
+        <v>4039</v>
       </c>
       <c r="C63" s="3">
         <v>10</v>
       </c>
       <c r="D63" s="5">
-        <v>45635.593055555553</v>
+        <v>45684.560416666667</v>
       </c>
       <c r="E63" s="6">
-        <v>45635.6</v>
+        <v>45684.567361111112</v>
       </c>
       <c r="F63" s="5">
-        <v>45635.595138888886</v>
-      </c>
-      <c r="G63" s="5">
-        <v>45642.524305555555</v>
+        <v>45684.5625</v>
+      </c>
+      <c r="G63" s="15">
+        <v>45691.40625</v>
       </c>
       <c r="H63" s="6">
-        <v>45642.520833333336</v>
-      </c>
+        <v>45691.404166666667</v>
+      </c>
+      <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B64" s="3">
-        <v>4323</v>
+        <v>5198</v>
       </c>
       <c r="C64" s="3">
         <v>10</v>
       </c>
       <c r="D64" s="5">
-        <v>45635.593055555553</v>
+        <v>45684.560416666667</v>
       </c>
       <c r="E64" s="6">
-        <v>45635.6</v>
+        <v>45684.567361111112</v>
       </c>
       <c r="F64" s="5">
-        <v>45635.595138888886</v>
-      </c>
-      <c r="G64" s="5">
-        <v>45642.524305555555</v>
+        <v>45684.5625</v>
+      </c>
+      <c r="G64" s="15">
+        <v>45691.40625</v>
       </c>
       <c r="H64" s="6">
-        <v>45642.520833333336</v>
-      </c>
+        <v>45691.404166666667</v>
+      </c>
+      <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B65" s="3">
-        <v>4218</v>
+        <v>4199</v>
       </c>
       <c r="C65" s="3">
         <v>10</v>
       </c>
       <c r="D65" s="5">
-        <v>45635.593055555553</v>
+        <v>45691.552777777775</v>
       </c>
       <c r="E65" s="6">
-        <v>45635.6</v>
+        <v>45691.55972222222</v>
       </c>
       <c r="F65" s="5">
-        <v>45635.595138888886</v>
-      </c>
-      <c r="G65" s="5">
-        <v>45642.524305555555</v>
+        <v>45691.554861111108</v>
+      </c>
+      <c r="G65" s="15">
+        <v>45700.553472222222</v>
       </c>
       <c r="H65" s="6">
-        <v>45640.560416666667</v>
-      </c>
-      <c r="I65" t="s">
-        <v>11</v>
-      </c>
+        <v>45700.551388888889</v>
+      </c>
+      <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C66" s="3"/>
+      <c r="A66" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B66" s="3">
+        <v>3954</v>
+      </c>
+      <c r="C66" s="3">
+        <v>10</v>
+      </c>
+      <c r="D66" s="5">
+        <v>45691.552777777775</v>
+      </c>
+      <c r="E66" s="6">
+        <v>45691.55972222222</v>
+      </c>
+      <c r="F66" s="5">
+        <v>45691.554861111108</v>
+      </c>
+      <c r="G66" s="15">
+        <v>45700.553472222222</v>
+      </c>
+      <c r="H66" s="6">
+        <v>45700.551388888889</v>
+      </c>
+      <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="B67" s="3">
-        <v>3982</v>
+        <v>5114</v>
       </c>
       <c r="C67" s="3">
         <v>10</v>
       </c>
       <c r="D67" s="5">
-        <v>45635.534722222219</v>
+        <v>45691.552777777775</v>
       </c>
       <c r="E67" s="6">
-        <v>45635.542361111111</v>
+        <v>45691.55972222222</v>
       </c>
       <c r="F67" s="5">
-        <v>45635.536805555559</v>
-      </c>
-      <c r="G67" s="5">
-        <v>45642.538194444445</v>
+        <v>45691.554861111108</v>
+      </c>
+      <c r="G67" s="15">
+        <v>45700.553472222222</v>
       </c>
       <c r="H67" s="6">
-        <v>45642.535416666666</v>
+        <v>45700.551388888889</v>
       </c>
       <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B68" s="3">
-        <v>4039</v>
+        <v>3982</v>
       </c>
       <c r="C68" s="3">
         <v>10</v>
       </c>
       <c r="D68" s="5">
-        <v>45635.534722222219</v>
+        <v>45691.557638888888</v>
       </c>
       <c r="E68" s="6">
-        <v>45635.542361111111</v>
+        <v>45691.571527777778</v>
       </c>
       <c r="F68" s="5">
-        <v>45635.536805555559</v>
-      </c>
-      <c r="G68" s="5">
-        <v>45642.538194444445</v>
+        <v>45691.559027777781</v>
+      </c>
+      <c r="G68" s="15">
+        <v>45700.569444444445</v>
       </c>
       <c r="H68" s="6">
-        <v>45642.535416666666</v>
+        <v>45700.567361111112</v>
       </c>
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B69" s="3">
-        <v>3954</v>
+        <v>4039</v>
       </c>
       <c r="C69" s="3">
         <v>10</v>
       </c>
       <c r="D69" s="5">
-        <v>45635.534722222219</v>
+        <v>45691.557638888888</v>
       </c>
       <c r="E69" s="6">
-        <v>45635.542361111111</v>
+        <v>45691.571527777778</v>
       </c>
       <c r="F69" s="5">
-        <v>45635.536805555559</v>
-      </c>
-      <c r="G69" s="5">
-        <v>45642.538194444445</v>
+        <v>45691.559027777781</v>
+      </c>
+      <c r="G69" s="15">
+        <v>45700.569444444445</v>
       </c>
       <c r="H69" s="6">
-        <v>45642.535416666666</v>
+        <v>45700.567361111112</v>
       </c>
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C70" s="3"/>
+      <c r="A70" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" s="3">
+        <v>5198</v>
+      </c>
+      <c r="C70" s="3">
+        <v>10</v>
+      </c>
+      <c r="D70" s="5">
+        <v>45691.557638888888</v>
+      </c>
+      <c r="E70" s="6">
+        <v>45691.571527777778</v>
+      </c>
+      <c r="F70" s="5">
+        <v>45691.559027777781</v>
+      </c>
+      <c r="G70" s="15">
+        <v>45700.569444444445</v>
+      </c>
+      <c r="H70" s="6">
+        <v>45700.567361111112</v>
+      </c>
+      <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B71" s="3">
-        <v>4199</v>
-      </c>
-      <c r="C71" s="3">
-        <v>10</v>
-      </c>
-      <c r="D71" s="5">
-        <v>45677.460416666669</v>
-      </c>
-      <c r="E71" s="6">
-        <v>45677.467361111114</v>
-      </c>
-      <c r="F71" s="5">
-        <v>45677.461805555555</v>
-      </c>
-      <c r="G71" s="5">
-        <v>45684.579861111109</v>
-      </c>
-      <c r="H71" s="6">
-        <v>45684.578472222223</v>
-      </c>
-      <c r="I71" s="4"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="3">
-        <v>3954</v>
-      </c>
-      <c r="C72" s="3">
-        <v>10</v>
-      </c>
-      <c r="D72" s="5">
-        <v>45677.460416666669</v>
-      </c>
-      <c r="E72" s="6">
-        <v>45677.467361111114</v>
-      </c>
-      <c r="F72" s="5">
-        <v>45677.461805555555</v>
-      </c>
-      <c r="G72" s="5">
-        <v>45684.579861111109</v>
-      </c>
-      <c r="H72" s="6">
-        <v>45684.578472222223</v>
-      </c>
-      <c r="I72" s="4"/>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B73" s="3">
-        <v>5114</v>
-      </c>
-      <c r="C73" s="3">
-        <v>10</v>
-      </c>
-      <c r="D73" s="5">
-        <v>45677.460416666669</v>
-      </c>
-      <c r="E73" s="6">
-        <v>45677.467361111114</v>
-      </c>
-      <c r="F73" s="5">
-        <v>45677.461805555555</v>
-      </c>
-      <c r="G73" s="5">
-        <v>45684.579861111109</v>
-      </c>
-      <c r="H73" s="6">
-        <v>45684.578472222223</v>
-      </c>
-      <c r="I73" s="4"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C74" s="3"/>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B75" s="3">
-        <v>3082</v>
-      </c>
-      <c r="C75" s="3">
-        <v>10</v>
-      </c>
-      <c r="D75" s="5">
-        <v>45677.473611111112</v>
-      </c>
-      <c r="E75" s="6">
-        <v>45677.480555555558</v>
-      </c>
-      <c r="F75" s="5">
-        <v>45677.475694444445</v>
-      </c>
-      <c r="G75" s="5">
-        <v>45684.40625</v>
-      </c>
-      <c r="H75" s="6">
-        <v>45684.404166666667</v>
-      </c>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B76" s="3">
-        <v>4039</v>
-      </c>
-      <c r="C76" s="3">
-        <v>10</v>
-      </c>
-      <c r="D76" s="5">
-        <v>45677.473611111112</v>
-      </c>
-      <c r="E76" s="6">
-        <v>45677.480555555558</v>
-      </c>
-      <c r="F76" s="5">
-        <v>45677.475694444445</v>
-      </c>
-      <c r="G76" s="5">
-        <v>45684.40625</v>
-      </c>
-      <c r="H76" s="6">
-        <v>45684.404166666667</v>
-      </c>
-      <c r="I76" s="4"/>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B77" s="3">
-        <v>5198</v>
-      </c>
-      <c r="C77" s="3">
-        <v>10</v>
-      </c>
-      <c r="D77" s="8"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="7"/>
-      <c r="I77" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C78" s="3"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B79" s="3">
-        <v>4199</v>
-      </c>
-      <c r="C79" s="3">
-        <v>10</v>
-      </c>
-      <c r="D79" s="5">
-        <v>45684.568055555559</v>
-      </c>
-      <c r="E79" s="6">
-        <v>45684.581944444442</v>
-      </c>
-      <c r="F79" s="5">
-        <v>45684.572916666664</v>
-      </c>
-      <c r="G79" s="5">
-        <v>45691.548611111109</v>
-      </c>
-      <c r="H79" s="6">
-        <v>45691.546527777777</v>
-      </c>
-      <c r="I79" s="4"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B80" s="3">
-        <v>3954</v>
-      </c>
-      <c r="C80" s="3">
-        <v>10</v>
-      </c>
-      <c r="D80" s="5">
-        <v>45684.568055555559</v>
-      </c>
-      <c r="E80" s="6">
-        <v>45684.581944444442</v>
-      </c>
-      <c r="F80" s="5">
-        <v>45684.572916666664</v>
-      </c>
-      <c r="G80" s="5">
-        <v>45691.548611111109</v>
-      </c>
-      <c r="H80" s="6">
-        <v>45691.546527777777</v>
-      </c>
-      <c r="I80" s="4"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B81" s="3">
-        <v>5114</v>
-      </c>
-      <c r="C81" s="3">
-        <v>10</v>
-      </c>
-      <c r="D81" s="8"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="7"/>
-      <c r="I81" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C82" s="3"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B83" s="3">
-        <v>3982</v>
-      </c>
-      <c r="C83" s="3">
-        <v>10</v>
-      </c>
-      <c r="D83" s="5">
-        <v>45684.560416666667</v>
-      </c>
-      <c r="E83" s="6">
-        <v>45684.567361111112</v>
-      </c>
-      <c r="F83" s="5">
-        <v>45684.5625</v>
-      </c>
-      <c r="G83" s="5">
-        <v>45691.40625</v>
-      </c>
-      <c r="H83" s="6">
-        <v>45691.404166666667</v>
-      </c>
-      <c r="I83" s="4"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A84" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B84" s="3">
-        <v>4039</v>
-      </c>
-      <c r="C84" s="3">
-        <v>10</v>
-      </c>
-      <c r="D84" s="5">
-        <v>45684.560416666667</v>
-      </c>
-      <c r="E84" s="6">
-        <v>45684.567361111112</v>
-      </c>
-      <c r="F84" s="5">
-        <v>45684.5625</v>
-      </c>
-      <c r="G84" s="5">
-        <v>45691.40625</v>
-      </c>
-      <c r="H84" s="6">
-        <v>45691.404166666667</v>
-      </c>
-      <c r="I84" s="4"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A85" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B85" s="3">
-        <v>5198</v>
-      </c>
-      <c r="C85" s="3">
-        <v>10</v>
-      </c>
-      <c r="D85" s="5">
-        <v>45684.560416666667</v>
-      </c>
-      <c r="E85" s="6">
-        <v>45684.567361111112</v>
-      </c>
-      <c r="F85" s="5">
-        <v>45684.5625</v>
-      </c>
-      <c r="G85" s="5">
-        <v>45691.40625</v>
-      </c>
-      <c r="H85" s="6">
-        <v>45691.404166666667</v>
-      </c>
-      <c r="I85" s="4"/>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C86" s="3"/>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A87" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B87" s="3">
-        <v>4199</v>
-      </c>
-      <c r="C87" s="3">
-        <v>10</v>
-      </c>
-      <c r="D87" s="5">
-        <v>45691.552777777775</v>
-      </c>
-      <c r="E87" s="6">
-        <v>45691.55972222222</v>
-      </c>
-      <c r="F87" s="5">
-        <v>45691.554861111108</v>
-      </c>
-      <c r="G87" s="5">
-        <v>45700.553472222222</v>
-      </c>
-      <c r="H87" s="6">
-        <v>45700.551388888889</v>
-      </c>
-      <c r="I87" s="4"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B88" s="3">
-        <v>3954</v>
-      </c>
-      <c r="C88" s="3">
-        <v>10</v>
-      </c>
-      <c r="D88" s="5">
-        <v>45691.552777777775</v>
-      </c>
-      <c r="E88" s="6">
-        <v>45691.55972222222</v>
-      </c>
-      <c r="F88" s="5">
-        <v>45691.554861111108</v>
-      </c>
-      <c r="G88" s="5">
-        <v>45700.553472222222</v>
-      </c>
-      <c r="H88" s="6">
-        <v>45700.551388888889</v>
-      </c>
-      <c r="I88" s="4"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B89" s="3">
-        <v>5114</v>
-      </c>
-      <c r="C89" s="3">
-        <v>10</v>
-      </c>
-      <c r="D89" s="5">
-        <v>45691.552777777775</v>
-      </c>
-      <c r="E89" s="6">
-        <v>45691.55972222222</v>
-      </c>
-      <c r="F89" s="5">
-        <v>45691.554861111108</v>
-      </c>
-      <c r="G89" s="5">
-        <v>45700.553472222222</v>
-      </c>
-      <c r="H89" s="6">
-        <v>45700.551388888889</v>
-      </c>
-      <c r="I89" s="4"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C90" s="3"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A91" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B91" s="3">
-        <v>3982</v>
-      </c>
-      <c r="C91" s="3">
-        <v>10</v>
-      </c>
-      <c r="D91" s="5">
-        <v>45691.557638888888</v>
-      </c>
-      <c r="E91" s="6">
-        <v>45691.571527777778</v>
-      </c>
-      <c r="F91" s="5">
-        <v>45691.559027777781</v>
-      </c>
-      <c r="G91" s="5">
-        <v>45700.569444444445</v>
-      </c>
-      <c r="H91" s="6">
-        <v>45700.567361111112</v>
-      </c>
-      <c r="I91" s="4"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A92" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B92" s="3">
-        <v>4039</v>
-      </c>
-      <c r="C92" s="3">
-        <v>10</v>
-      </c>
-      <c r="D92" s="5">
-        <v>45691.557638888888</v>
-      </c>
-      <c r="E92" s="6">
-        <v>45691.571527777778</v>
-      </c>
-      <c r="F92" s="5">
-        <v>45691.559027777781</v>
-      </c>
-      <c r="G92" s="5">
-        <v>45700.569444444445</v>
-      </c>
-      <c r="H92" s="6">
-        <v>45700.567361111112</v>
-      </c>
-      <c r="I92" s="4"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A93" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B93" s="3">
-        <v>5198</v>
-      </c>
-      <c r="C93" s="3">
-        <v>10</v>
-      </c>
-      <c r="D93" s="5">
-        <v>45691.557638888888</v>
-      </c>
-      <c r="E93" s="6">
-        <v>45691.571527777778</v>
-      </c>
-      <c r="F93" s="5">
-        <v>45691.559027777781</v>
-      </c>
-      <c r="G93" s="5">
-        <v>45700.569444444445</v>
-      </c>
-      <c r="H93" s="6">
-        <v>45700.567361111112</v>
-      </c>
-      <c r="I93" s="4"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C94" s="3"/>
+      <c r="C71" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/Study_dates_MeLiDos_FUSPCEU.xlsx
+++ b/data/Study_dates_MeLiDos_FUSPCEU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/WP2.2.5_Data_Analysis/BaezaEtAl_Dataset_2025/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/BaezaEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D366736-3556-D349-9C95-1CDFB0AB3F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B35990-6941-4A4C-8FDC-E4C943B918B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="58180" yWindow="9380" windowWidth="29040" windowHeight="15840" xr2:uid="{EB2C5E3B-016F-4147-BA32-349D8E1D3953}"/>
   </bookViews>
@@ -288,7 +288,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="d/m/yy\ h:mm;@"/>
+    <numFmt numFmtId="164" formatCode="d/m/yy\ h:mm;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -364,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -382,12 +382,6 @@
     <xf numFmtId="22" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="22" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="22" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -399,13 +393,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -747,11 +741,11 @@
   <cols>
     <col min="1" max="2" width="23" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="23" style="11" customWidth="1"/>
-    <col min="5" max="5" width="23" style="12" customWidth="1"/>
-    <col min="6" max="6" width="23" style="11" customWidth="1"/>
-    <col min="7" max="7" width="23" style="16" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" style="9" customWidth="1"/>
+    <col min="5" max="5" width="23" style="10" customWidth="1"/>
+    <col min="6" max="6" width="23" style="9" customWidth="1"/>
+    <col min="7" max="7" width="23" style="14" customWidth="1"/>
+    <col min="8" max="8" width="23.6640625" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -764,19 +758,19 @@
       <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -802,7 +796,7 @@
       <c r="F2" s="5">
         <v>45572.673611111109</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="13">
         <v>45579.583333333336</v>
       </c>
       <c r="H2" s="6">
@@ -829,7 +823,7 @@
       <c r="F3" s="5">
         <v>45572.673611111109</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="13">
         <v>45579.583333333336</v>
       </c>
       <c r="H3" s="6">
@@ -856,7 +850,7 @@
       <c r="F4" s="5">
         <v>45572.673611111109</v>
       </c>
-      <c r="G4" s="15">
+      <c r="G4" s="13">
         <v>45579.583333333336</v>
       </c>
       <c r="H4" s="6">
@@ -883,7 +877,7 @@
       <c r="F5" s="5">
         <v>45572.630555555559</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="13">
         <v>45579.576388888891</v>
       </c>
       <c r="H5" s="6">
@@ -910,7 +904,7 @@
       <c r="F6" s="5">
         <v>45572.630555555559</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="13">
         <v>45579.576388888891</v>
       </c>
       <c r="H6" s="6">
@@ -937,7 +931,7 @@
       <c r="F7" s="5">
         <v>45572.630555555559</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="13">
         <v>45579.576388888891</v>
       </c>
       <c r="H7" s="6">
@@ -964,7 +958,7 @@
       <c r="F8" s="5">
         <v>45579.583333333336</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="13">
         <v>45586.548611111109</v>
       </c>
       <c r="H8" s="6">
@@ -991,7 +985,7 @@
       <c r="F9" s="5">
         <v>45579.583333333336</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="13">
         <v>45586.548611111109</v>
       </c>
       <c r="H9" s="6">
@@ -1018,7 +1012,7 @@
       <c r="F10" s="5">
         <v>45579.583333333336</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="13">
         <v>45586.548611111109</v>
       </c>
       <c r="H10" s="6">
@@ -1045,7 +1039,7 @@
       <c r="F11" s="5">
         <v>45579.567361111112</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="13">
         <v>45586.554861111108</v>
       </c>
       <c r="H11" s="6">
@@ -1072,7 +1066,7 @@
       <c r="F12" s="5">
         <v>45579.567361111112</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="13">
         <v>45586.554861111108</v>
       </c>
       <c r="H12" s="6">
@@ -1099,7 +1093,7 @@
       <c r="F13" s="5">
         <v>45579.567361111112</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="13">
         <v>45586.554861111108</v>
       </c>
       <c r="H13" s="6">
@@ -1126,7 +1120,7 @@
       <c r="F14" s="5">
         <v>45586.534722222219</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="13">
         <v>45593.798611111109</v>
       </c>
       <c r="H14" s="6">
@@ -1153,7 +1147,7 @@
       <c r="F15" s="5">
         <v>45586.534722222219</v>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="13">
         <v>45593.798611111109</v>
       </c>
       <c r="H15" s="6">
@@ -1180,7 +1174,7 @@
       <c r="F16" s="5">
         <v>45586.534722222219</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="13">
         <v>45593.798611111109</v>
       </c>
       <c r="H16" s="6">
@@ -1207,7 +1201,7 @@
       <c r="F17" s="5">
         <v>45586.551388888889</v>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="13">
         <v>45593.84375</v>
       </c>
       <c r="H17" s="6">
@@ -1234,7 +1228,7 @@
       <c r="F18" s="5">
         <v>45586.551388888889</v>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="13">
         <v>45593.84375</v>
       </c>
       <c r="H18" s="6">
@@ -1261,7 +1255,7 @@
       <c r="F19" s="5">
         <v>45586.551388888889</v>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="13">
         <v>45593.84375</v>
       </c>
       <c r="H19" s="6">
@@ -1288,7 +1282,7 @@
       <c r="F20" s="5">
         <v>45599.897222222222</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="13">
         <v>45607.413194444445</v>
       </c>
       <c r="H20" s="6">
@@ -1315,7 +1309,7 @@
       <c r="F21" s="5">
         <v>45599.897222222222</v>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="13">
         <v>45607.413194444445</v>
       </c>
       <c r="H21" s="6">
@@ -1342,7 +1336,7 @@
       <c r="F22" s="5">
         <v>45599.897222222222</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="13">
         <v>45607.413194444445</v>
       </c>
       <c r="H22" s="6">
@@ -1369,7 +1363,7 @@
       <c r="F23" s="5">
         <v>45599.808333333334</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="13">
         <v>45604.482638888891</v>
       </c>
       <c r="H23" s="6">
@@ -1398,7 +1392,7 @@
       <c r="F24" s="5">
         <v>45599.808333333334</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="13">
         <v>45604.482638888891</v>
       </c>
       <c r="H24" s="6">
@@ -1425,7 +1419,7 @@
       <c r="F25" s="5">
         <v>45599.808333333334</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="13">
         <v>45604.482638888891</v>
       </c>
       <c r="H25" s="6">
@@ -1452,7 +1446,7 @@
       <c r="F26" s="5">
         <v>45607.579861111109</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="13">
         <v>45614.552083333336</v>
       </c>
       <c r="H26" s="6">
@@ -1479,7 +1473,7 @@
       <c r="F27" s="5">
         <v>45607.579861111109</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="13">
         <v>45614.552083333336</v>
       </c>
       <c r="H27" s="6">
@@ -1506,7 +1500,7 @@
       <c r="F28" s="5">
         <v>45607.579861111109</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="13">
         <v>45614.552083333336</v>
       </c>
       <c r="H28" s="6">
@@ -1533,7 +1527,7 @@
       <c r="F29" s="5">
         <v>45628.518750000003</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="13">
         <v>45635.59375</v>
       </c>
       <c r="H29" s="6">
@@ -1560,7 +1554,7 @@
       <c r="F30" s="5">
         <v>45628.518750000003</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="13">
         <v>45635.59375</v>
       </c>
       <c r="H30" s="6">
@@ -1587,7 +1581,7 @@
       <c r="F31" s="5">
         <v>45628.518750000003</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="13">
         <v>45635.59375</v>
       </c>
       <c r="H31" s="6">
@@ -1614,7 +1608,7 @@
       <c r="F32" s="5">
         <v>45614.5625</v>
       </c>
-      <c r="G32" s="15">
+      <c r="G32" s="13">
         <v>45621.524305555555</v>
       </c>
       <c r="H32" s="6">
@@ -1641,7 +1635,7 @@
       <c r="F33" s="5">
         <v>45614.5625</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="13">
         <v>45621.524305555555</v>
       </c>
       <c r="H33" s="6">
@@ -1668,7 +1662,7 @@
       <c r="F34" s="5">
         <v>45614.5625</v>
       </c>
-      <c r="G34" s="15">
+      <c r="G34" s="13">
         <v>45621.524305555555</v>
       </c>
       <c r="H34" s="6">
@@ -1683,7 +1677,7 @@
       <c r="B35" s="3">
         <v>3910</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="11">
         <v>60</v>
       </c>
       <c r="D35" s="5">
@@ -1695,7 +1689,7 @@
       <c r="F35" s="5">
         <v>45614.559027777781</v>
       </c>
-      <c r="G35" s="15">
+      <c r="G35" s="13">
         <v>45621.388888888891</v>
       </c>
       <c r="H35" s="6">
@@ -1724,7 +1718,7 @@
       <c r="F36" s="5">
         <v>45614.559027777781</v>
       </c>
-      <c r="G36" s="15">
+      <c r="G36" s="13">
         <v>45621.388888888891</v>
       </c>
       <c r="H36" s="6">
@@ -1751,7 +1745,7 @@
       <c r="F37" s="5">
         <v>45614.559027777781</v>
       </c>
-      <c r="G37" s="15">
+      <c r="G37" s="13">
         <v>45621.388888888891</v>
       </c>
       <c r="H37" s="6">
@@ -1778,7 +1772,7 @@
       <c r="F38" s="5">
         <v>45621.578472222223</v>
       </c>
-      <c r="G38" s="15">
+      <c r="G38" s="13">
         <v>45628.504166666666</v>
       </c>
       <c r="H38" s="6">
@@ -1805,7 +1799,7 @@
       <c r="F39" s="5">
         <v>45621.578472222223</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="13">
         <v>45628.504166666666</v>
       </c>
       <c r="H39" s="6">
@@ -1832,7 +1826,7 @@
       <c r="F40" s="5">
         <v>45621.578472222223</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="13">
         <v>45628.504166666666</v>
       </c>
       <c r="H40" s="6">
@@ -1859,7 +1853,7 @@
       <c r="F41" s="5">
         <v>45621.5625</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="13">
         <v>45628.541666666664</v>
       </c>
       <c r="H41" s="6">
@@ -1886,7 +1880,7 @@
       <c r="F42" s="5">
         <v>45621.5625</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="13">
         <v>45628.541666666664</v>
       </c>
       <c r="H42" s="6">
@@ -1913,7 +1907,7 @@
       <c r="F43" s="5">
         <v>45621.5625</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="13">
         <v>45628.541666666664</v>
       </c>
       <c r="H43" s="6">
@@ -1940,7 +1934,7 @@
       <c r="F44" s="5">
         <v>45628.54583333333</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="13">
         <v>45635.529166666667</v>
       </c>
       <c r="H44" s="6">
@@ -1967,7 +1961,7 @@
       <c r="F45" s="5">
         <v>45628.54583333333</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="13">
         <v>45635.529166666667</v>
       </c>
       <c r="H45" s="6">
@@ -1994,7 +1988,7 @@
       <c r="F46" s="5">
         <v>45628.54583333333</v>
       </c>
-      <c r="G46" s="15">
+      <c r="G46" s="13">
         <v>45635.529166666667</v>
       </c>
       <c r="H46" s="6">
@@ -2021,7 +2015,7 @@
       <c r="F47" s="5">
         <v>45635.595138888886</v>
       </c>
-      <c r="G47" s="15">
+      <c r="G47" s="13">
         <v>45642.524305555555</v>
       </c>
       <c r="H47" s="6">
@@ -2047,7 +2041,7 @@
       <c r="F48" s="5">
         <v>45635.595138888886</v>
       </c>
-      <c r="G48" s="15">
+      <c r="G48" s="13">
         <v>45642.524305555555</v>
       </c>
       <c r="H48" s="6">
@@ -2073,7 +2067,7 @@
       <c r="F49" s="5">
         <v>45635.595138888886</v>
       </c>
-      <c r="G49" s="15">
+      <c r="G49" s="13">
         <v>45642.524305555555</v>
       </c>
       <c r="H49" s="6">
@@ -2102,7 +2096,7 @@
       <c r="F50" s="5">
         <v>45635.536805555559</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="13">
         <v>45642.538194444445</v>
       </c>
       <c r="H50" s="6">
@@ -2129,7 +2123,7 @@
       <c r="F51" s="5">
         <v>45635.536805555559</v>
       </c>
-      <c r="G51" s="15">
+      <c r="G51" s="13">
         <v>45642.538194444445</v>
       </c>
       <c r="H51" s="6">
@@ -2156,7 +2150,7 @@
       <c r="F52" s="5">
         <v>45635.536805555559</v>
       </c>
-      <c r="G52" s="15">
+      <c r="G52" s="13">
         <v>45642.538194444445</v>
       </c>
       <c r="H52" s="6">
@@ -2183,7 +2177,7 @@
       <c r="F53" s="5">
         <v>45677.461805555555</v>
       </c>
-      <c r="G53" s="15">
+      <c r="G53" s="13">
         <v>45684.579861111109</v>
       </c>
       <c r="H53" s="6">
@@ -2210,7 +2204,7 @@
       <c r="F54" s="5">
         <v>45677.461805555555</v>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="13">
         <v>45684.579861111109</v>
       </c>
       <c r="H54" s="6">
@@ -2237,7 +2231,7 @@
       <c r="F55" s="5">
         <v>45677.461805555555</v>
       </c>
-      <c r="G55" s="15">
+      <c r="G55" s="13">
         <v>45684.579861111109</v>
       </c>
       <c r="H55" s="6">
@@ -2264,7 +2258,7 @@
       <c r="F56" s="5">
         <v>45677.475694444445</v>
       </c>
-      <c r="G56" s="15">
+      <c r="G56" s="13">
         <v>45684.40625</v>
       </c>
       <c r="H56" s="6">
@@ -2291,7 +2285,7 @@
       <c r="F57" s="5">
         <v>45677.475694444445</v>
       </c>
-      <c r="G57" s="15">
+      <c r="G57" s="13">
         <v>45684.40625</v>
       </c>
       <c r="H57" s="6">
@@ -2309,10 +2303,21 @@
       <c r="C58" s="3">
         <v>10</v>
       </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="8"/>
-      <c r="H58" s="7"/>
+      <c r="D58" s="5">
+        <v>45677.473611111112</v>
+      </c>
+      <c r="E58" s="6">
+        <v>45677.480555555558</v>
+      </c>
+      <c r="F58" s="5">
+        <v>45677.475694444445</v>
+      </c>
+      <c r="G58" s="13">
+        <v>45684.40625</v>
+      </c>
+      <c r="H58" s="6">
+        <v>45684.404166666667</v>
+      </c>
       <c r="I58" t="s">
         <v>12</v>
       </c>
@@ -2336,7 +2341,7 @@
       <c r="F59" s="5">
         <v>45684.572916666664</v>
       </c>
-      <c r="G59" s="15">
+      <c r="G59" s="13">
         <v>45691.548611111109</v>
       </c>
       <c r="H59" s="6">
@@ -2363,7 +2368,7 @@
       <c r="F60" s="5">
         <v>45684.572916666664</v>
       </c>
-      <c r="G60" s="15">
+      <c r="G60" s="13">
         <v>45691.548611111109</v>
       </c>
       <c r="H60" s="6">
@@ -2381,10 +2386,21 @@
       <c r="C61" s="3">
         <v>10</v>
       </c>
-      <c r="D61" s="8"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="8"/>
-      <c r="H61" s="7"/>
+      <c r="D61" s="5">
+        <v>45684.568055555559</v>
+      </c>
+      <c r="E61" s="6">
+        <v>45684.581944444442</v>
+      </c>
+      <c r="F61" s="5">
+        <v>45684.572916666664</v>
+      </c>
+      <c r="G61" s="13">
+        <v>45691.548611111109</v>
+      </c>
+      <c r="H61" s="6">
+        <v>45691.546527777777</v>
+      </c>
       <c r="I61" t="s">
         <v>12</v>
       </c>
@@ -2408,7 +2424,7 @@
       <c r="F62" s="5">
         <v>45684.5625</v>
       </c>
-      <c r="G62" s="15">
+      <c r="G62" s="13">
         <v>45691.40625</v>
       </c>
       <c r="H62" s="6">
@@ -2435,7 +2451,7 @@
       <c r="F63" s="5">
         <v>45684.5625</v>
       </c>
-      <c r="G63" s="15">
+      <c r="G63" s="13">
         <v>45691.40625</v>
       </c>
       <c r="H63" s="6">
@@ -2462,7 +2478,7 @@
       <c r="F64" s="5">
         <v>45684.5625</v>
       </c>
-      <c r="G64" s="15">
+      <c r="G64" s="13">
         <v>45691.40625</v>
       </c>
       <c r="H64" s="6">
@@ -2489,7 +2505,7 @@
       <c r="F65" s="5">
         <v>45691.554861111108</v>
       </c>
-      <c r="G65" s="15">
+      <c r="G65" s="13">
         <v>45700.553472222222</v>
       </c>
       <c r="H65" s="6">
@@ -2516,7 +2532,7 @@
       <c r="F66" s="5">
         <v>45691.554861111108</v>
       </c>
-      <c r="G66" s="15">
+      <c r="G66" s="13">
         <v>45700.553472222222</v>
       </c>
       <c r="H66" s="6">
@@ -2543,7 +2559,7 @@
       <c r="F67" s="5">
         <v>45691.554861111108</v>
       </c>
-      <c r="G67" s="15">
+      <c r="G67" s="13">
         <v>45700.553472222222</v>
       </c>
       <c r="H67" s="6">
@@ -2570,7 +2586,7 @@
       <c r="F68" s="5">
         <v>45691.559027777781</v>
       </c>
-      <c r="G68" s="15">
+      <c r="G68" s="13">
         <v>45700.569444444445</v>
       </c>
       <c r="H68" s="6">
@@ -2597,7 +2613,7 @@
       <c r="F69" s="5">
         <v>45691.559027777781</v>
       </c>
-      <c r="G69" s="15">
+      <c r="G69" s="13">
         <v>45700.569444444445</v>
       </c>
       <c r="H69" s="6">
@@ -2624,7 +2640,7 @@
       <c r="F70" s="5">
         <v>45691.559027777781</v>
       </c>
-      <c r="G70" s="15">
+      <c r="G70" s="13">
         <v>45700.569444444445</v>
       </c>
       <c r="H70" s="6">

--- a/data/Study_dates_MeLiDos_FUSPCEU.xlsx
+++ b/data/Study_dates_MeLiDos_FUSPCEU.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/BaezaEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B35990-6941-4A4C-8FDC-E4C943B918B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24ABC24A-F380-EF46-8DBC-FF17A823B68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="58180" yWindow="9380" windowWidth="29040" windowHeight="15840" xr2:uid="{EB2C5E3B-016F-4147-BA32-349D8E1D3953}"/>
   </bookViews>
@@ -2509,7 +2509,7 @@
         <v>45700.553472222222</v>
       </c>
       <c r="H65" s="6">
-        <v>45700.551388888889</v>
+        <v>45698.551388888889</v>
       </c>
       <c r="I65" s="4"/>
     </row>
@@ -2536,7 +2536,7 @@
         <v>45700.553472222222</v>
       </c>
       <c r="H66" s="6">
-        <v>45700.551388888889</v>
+        <v>45698.551388888889</v>
       </c>
       <c r="I66" s="4"/>
     </row>
@@ -2563,7 +2563,7 @@
         <v>45700.553472222222</v>
       </c>
       <c r="H67" s="6">
-        <v>45700.551388888889</v>
+        <v>45698.551388888889</v>
       </c>
       <c r="I67" s="4"/>
     </row>
@@ -2590,7 +2590,7 @@
         <v>45700.569444444445</v>
       </c>
       <c r="H68" s="6">
-        <v>45700.567361111112</v>
+        <v>45698.567361111112</v>
       </c>
       <c r="I68" s="4"/>
     </row>
@@ -2617,7 +2617,7 @@
         <v>45700.569444444445</v>
       </c>
       <c r="H69" s="6">
-        <v>45700.567361111112</v>
+        <v>45698.567361111112</v>
       </c>
       <c r="I69" s="4"/>
     </row>
@@ -2644,7 +2644,7 @@
         <v>45700.569444444445</v>
       </c>
       <c r="H70" s="6">
-        <v>45700.567361111112</v>
+        <v>45698.567361111112</v>
       </c>
       <c r="I70" s="4"/>
     </row>
